--- a/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/RIC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_144832.xlsx
+++ b/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/RIC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_144832.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uetpk-my.sharepoint.com/personal/adeel_munir_uet_edu_pk/Documents/Drive G/Data science coding/VSCode programming/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_803CB43E513C8B2211C895FAA9C4C7BA4ECF81ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_803CB43E513C8B2211C895FAA9C4C7BA4ECF81ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1028543D-A627-4926-A555-8556C8A86F8F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Original_Responses" sheetId="1" r:id="rId1"/>
@@ -1002,6 +1002,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="63.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3424,6 +3430,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="220.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
